--- a/NECP Scenario/Results/Regional Results/EL51_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL51_Generation.xlsx
@@ -537,25 +537,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.547324155240916E-12</v>
+        <v>2.284563549474818E-12</v>
       </c>
       <c r="C2">
-        <v>8.102391357598158E-13</v>
+        <v>1.196284665126506E-12</v>
       </c>
       <c r="D2">
-        <v>1.190476559942658E-12</v>
+        <v>1.757693474345201E-12</v>
       </c>
       <c r="E2">
-        <v>1.749244803285862E-12</v>
+        <v>2.582696531636748E-12</v>
       </c>
       <c r="F2">
-        <v>2.570234414878476E-12</v>
+        <v>3.794856143730565E-12</v>
       </c>
       <c r="G2">
-        <v>3.776457277571469E-12</v>
+        <v>5.575805719189174E-12</v>
       </c>
       <c r="H2">
-        <v>2.288763356054221E-11</v>
+        <v>3.379291906619893E-11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5.465853241953663E-08</v>
+        <v>8.031648522407096E-08</v>
       </c>
       <c r="C3">
-        <v>4.939401994079955E-08</v>
+        <v>7.341027224565221E-08</v>
       </c>
       <c r="D3">
-        <v>1.315841864236243E-07</v>
+        <v>1.926445554408513E-07</v>
       </c>
       <c r="E3">
-        <v>2.783965222858995E-07</v>
+        <v>3.785417597076638E-07</v>
       </c>
       <c r="F3">
-        <v>1.021928270728677E-06</v>
+        <v>1.367736234682176E-06</v>
       </c>
       <c r="G3">
-        <v>5.476328451811136E-06</v>
+        <v>4.593011006406291E-06</v>
       </c>
       <c r="H3">
-        <v>0.2230094443859137</v>
+        <v>0.4900106898878916</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.645975255907551E-08</v>
+        <v>6.826901244254765E-08</v>
       </c>
       <c r="C4">
-        <v>4.198491695526323E-08</v>
+        <v>6.239873141233837E-08</v>
       </c>
       <c r="D4">
-        <v>1.118465584656892E-07</v>
+        <v>1.637478721282745E-07</v>
       </c>
       <c r="E4">
-        <v>2.366370439494329E-07</v>
+        <v>3.217604957557613E-07</v>
       </c>
       <c r="F4">
-        <v>8.686390301257668E-07</v>
+        <v>1.162575799484074E-06</v>
       </c>
       <c r="G4">
-        <v>4.65487918404587E-06</v>
+        <v>3.904059355449589E-06</v>
       </c>
       <c r="H4">
-        <v>0.1895580277280154</v>
+        <v>0.4165090864046846</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,22 +618,22 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.2697175661287808</v>
+        <v>0.529420026319424</v>
       </c>
       <c r="D5">
-        <v>0.2690172652867593</v>
+        <v>0.5273402534125746</v>
       </c>
       <c r="E5">
-        <v>0.6064170411078996</v>
+        <v>0.6064144436990166</v>
       </c>
       <c r="F5">
-        <v>0.6645997668116334</v>
+        <v>0.6653699088991538</v>
       </c>
       <c r="G5">
-        <v>0.7202497500223166</v>
+        <v>0.7216507898871394</v>
       </c>
       <c r="H5">
-        <v>0.7750372636898365</v>
+        <v>0.776029131291988</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -667,25 +667,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.208497511570749</v>
+        <v>0.2086356752760454</v>
       </c>
       <c r="C7">
-        <v>0.9764846539470632</v>
+        <v>1.718486107072929</v>
       </c>
       <c r="D7">
-        <v>0.9551405993920524</v>
+        <v>1.693316597418909</v>
       </c>
       <c r="E7">
-        <v>1.90297222363907</v>
+        <v>1.90297222339458</v>
       </c>
       <c r="F7">
-        <v>2.058444445964789</v>
+        <v>2.058444445708004</v>
       </c>
       <c r="G7">
-        <v>2.206847223371053</v>
+        <v>2.206847223258248</v>
       </c>
       <c r="H7">
-        <v>2.355249990212576</v>
+        <v>2.355249989305817</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -719,25 +719,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.07290122781821325</v>
+        <v>0.07294953680430201</v>
       </c>
       <c r="C9">
-        <v>0.07171063455006892</v>
+        <v>0.07144924188504745</v>
       </c>
       <c r="D9">
-        <v>0.0649479792531409</v>
+        <v>0.06472848693942992</v>
       </c>
       <c r="E9">
-        <v>0.05895786225819431</v>
+        <v>0.05896045957956792</v>
       </c>
       <c r="F9">
-        <v>0.05513605344956759</v>
+        <v>0.05436591126933719</v>
       </c>
       <c r="G9">
-        <v>0.05137515324515392</v>
+        <v>0.04997411333658267</v>
       </c>
       <c r="H9">
-        <v>0.04847671884688592</v>
+        <v>0.0474848509014099</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -748,22 +748,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>8.075771043971585E-08</v>
+        <v>1.184586099418227E-07</v>
       </c>
       <c r="D10">
-        <v>8.591165579194367E-08</v>
+        <v>1.323163868802513E-07</v>
       </c>
       <c r="E10">
-        <v>1.256683975017398E-07</v>
+        <v>1.869432427606098E-07</v>
       </c>
       <c r="F10">
-        <v>9.821457444116976E-08</v>
+        <v>1.478413618047863E-07</v>
       </c>
       <c r="G10">
-        <v>9.161340686350944E-08</v>
+        <v>1.379499072666037E-07</v>
       </c>
       <c r="H10">
-        <v>3.981484113160747E-07</v>
+        <v>5.978796761180695E-07</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -771,13 +771,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.267245864594498</v>
+        <v>1.271246826205071</v>
       </c>
       <c r="C11">
-        <v>1.318445551925797</v>
+        <v>1.309434839087322</v>
       </c>
       <c r="D11">
-        <v>1.291591177642838</v>
+        <v>1.290785291941583</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.491115233480913</v>
+        <v>2.491115235948175</v>
       </c>
       <c r="C14">
-        <v>2.530674431811742</v>
+        <v>2.530674430446548</v>
       </c>
       <c r="D14">
-        <v>2.782446422762697</v>
+        <v>2.782446412498694</v>
       </c>
       <c r="E14">
-        <v>3.322611658856318</v>
+        <v>3.322611205335802</v>
       </c>
       <c r="F14">
-        <v>4.012584213483361</v>
+        <v>3.46652257059696</v>
       </c>
       <c r="G14">
-        <v>3.994945384670847</v>
+        <v>3.994945409311497</v>
       </c>
       <c r="H14">
-        <v>5.193479755120991</v>
+        <v>5.193479922218667</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -953,25 +953,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.6002002212963943</v>
+        <v>0.5876502437979866</v>
       </c>
       <c r="C18">
-        <v>0.7427716095337483</v>
+        <v>0.755900097417767</v>
       </c>
       <c r="D18">
-        <v>1.096219107413881</v>
+        <v>1.097311289187966</v>
       </c>
       <c r="E18">
-        <v>1.052691364282882</v>
+        <v>1.018372483623811</v>
       </c>
       <c r="F18">
-        <v>1.094858010693851</v>
+        <v>1.094354616125651</v>
       </c>
       <c r="G18">
-        <v>1.230145839577852</v>
+        <v>1.216818251639666</v>
       </c>
       <c r="H18">
-        <v>1.179601804423188</v>
+        <v>1.181757932020471</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -979,25 +979,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4.639902156315829E-08</v>
+        <v>6.821770960755141E-08</v>
       </c>
       <c r="C19">
-        <v>4.514340130154077E-08</v>
+        <v>6.721877603532261E-08</v>
       </c>
       <c r="D19">
-        <v>9.320743038470307E-08</v>
+        <v>1.376554893097102E-07</v>
       </c>
       <c r="E19">
-        <v>2.441427872913312E-07</v>
+        <v>3.278601428230043E-07</v>
       </c>
       <c r="F19">
-        <v>5.94809550356125E-07</v>
+        <v>8.08647828727162E-07</v>
       </c>
       <c r="G19">
-        <v>1.032555885164036E-06</v>
+        <v>1.420178725057439E-06</v>
       </c>
       <c r="H19">
-        <v>4.176988603028132E-06</v>
+        <v>6.504119008651761E-06</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1005,25 +1005,25 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.4801601770403334</v>
+        <v>0.4701201950417137</v>
       </c>
       <c r="C20">
-        <v>0.5942172876187015</v>
+        <v>0.6047200779341912</v>
       </c>
       <c r="D20">
-        <v>0.8769752859340836</v>
+        <v>0.8778490313507773</v>
       </c>
       <c r="E20">
-        <v>0.8421530914229242</v>
+        <v>0.8146979868985657</v>
       </c>
       <c r="F20">
-        <v>0.8758864085540983</v>
+        <v>0.8754836929012499</v>
       </c>
       <c r="G20">
-        <v>0.9841166716575613</v>
+        <v>0.9734546013126497</v>
       </c>
       <c r="H20">
-        <v>0.9436814435348959</v>
+        <v>0.9454063456145224</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1031,25 +1031,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3.711921725436899E-08</v>
+        <v>5.457416768938511E-08</v>
       </c>
       <c r="C21">
-        <v>3.611472104123267E-08</v>
+        <v>5.377502082825808E-08</v>
       </c>
       <c r="D21">
-        <v>7.456594430776245E-08</v>
+        <v>1.101243914477682E-07</v>
       </c>
       <c r="E21">
-        <v>1.95314229833065E-07</v>
+        <v>2.622881142584037E-07</v>
       </c>
       <c r="F21">
-        <v>4.758476402849003E-07</v>
+        <v>6.469182629817297E-07</v>
       </c>
       <c r="G21">
-        <v>8.260447081312295E-07</v>
+        <v>1.136142980045951E-06</v>
       </c>
       <c r="H21">
-        <v>3.341590882422506E-06</v>
+        <v>5.203295206921407E-06</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1060,22 +1060,22 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>1.310392853051065E-08</v>
+        <v>1.94541973574551E-08</v>
       </c>
       <c r="D22">
-        <v>1.891327447091216E-08</v>
+        <v>2.921122949802947E-08</v>
       </c>
       <c r="E22">
-        <v>1.414159093337646E-07</v>
+        <v>3.045564411043749E-07</v>
       </c>
       <c r="F22">
-        <v>0.09622728239389157</v>
+        <v>0.09622728257324027</v>
       </c>
       <c r="G22">
-        <v>0.09622728318452588</v>
+        <v>0.09622728326269168</v>
       </c>
       <c r="H22">
-        <v>0.09622728244274684</v>
+        <v>0.09622728191607231</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1083,25 +1083,25 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.1578267926909776</v>
+        <v>0.1578267926496841</v>
       </c>
       <c r="C23">
-        <v>0.1578267927271661</v>
+        <v>0.1578267927034451</v>
       </c>
       <c r="D23">
-        <v>0.1578267927027968</v>
+        <v>0.1578267926676198</v>
       </c>
       <c r="E23">
-        <v>0.1578267926805092</v>
+        <v>0.1578267926325987</v>
       </c>
       <c r="F23">
-        <v>0.1578267926489856</v>
+        <v>0.157826792586199</v>
       </c>
       <c r="G23">
-        <v>0.1578267925847059</v>
+        <v>0.1578267924940215</v>
       </c>
       <c r="H23">
-        <v>0.1578267914756697</v>
+        <v>0.157826790890431</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1109,25 +1109,25 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.648543864177383</v>
+        <v>2.656905877378865</v>
       </c>
       <c r="C24">
-        <v>2.755551345443326</v>
+        <v>2.736719021918937</v>
       </c>
       <c r="D24">
-        <v>2.699425712043639</v>
+        <v>2.697741491931192</v>
       </c>
       <c r="E24">
-        <v>2.187856911591135E-07</v>
+        <v>3.253170826004048E-07</v>
       </c>
       <c r="F24">
-        <v>1.735781049862013E-07</v>
+        <v>2.609510103453171E-07</v>
       </c>
       <c r="G24">
-        <v>1.649354192996216E-07</v>
+        <v>2.479524248646795E-07</v>
       </c>
       <c r="H24">
-        <v>7.305583110833765E-07</v>
+        <v>1.095156938761672E-06</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1135,25 +1135,25 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2.569107423335578E-09</v>
+        <v>3.798348083561596E-09</v>
       </c>
       <c r="C25">
-        <v>2.241353421372519E-09</v>
+        <v>3.305416394971371E-09</v>
       </c>
       <c r="D25">
-        <v>2.615856833509311E-09</v>
+        <v>3.872445900308602E-09</v>
       </c>
       <c r="E25">
-        <v>3.646450630744981E-09</v>
+        <v>5.371769339342842E-09</v>
       </c>
       <c r="F25">
-        <v>4.124672108785196E-09</v>
+        <v>6.08911625567359E-09</v>
       </c>
       <c r="G25">
-        <v>4.923995323279695E-09</v>
+        <v>7.269789259431301E-09</v>
       </c>
       <c r="H25">
-        <v>2.772687693192611E-08</v>
+        <v>4.096220384974007E-08</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1190,22 +1190,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>1.21463158627793E-08</v>
+        <v>1.785680553858327E-08</v>
       </c>
       <c r="D27">
-        <v>4.906714756320742E-08</v>
+        <v>7.313852835428719E-08</v>
       </c>
       <c r="E27">
-        <v>5.465702395092806E-07</v>
+        <v>8.191804706645766E-07</v>
       </c>
       <c r="F27">
-        <v>1.071328649632913</v>
+        <v>1.170718247505194</v>
       </c>
       <c r="G27">
-        <v>2.258575881540857</v>
+        <v>1.919004250801437</v>
       </c>
       <c r="H27">
-        <v>4.96558404242285</v>
+        <v>4.864239998265808</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1268,22 +1268,22 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0.4960471957894129</v>
+        <v>0.4342338301866057</v>
       </c>
       <c r="D30">
-        <v>0.6964652383780422</v>
+        <v>0.5685347947139183</v>
       </c>
       <c r="E30">
-        <v>0.6733124042908555</v>
+        <v>0.5465622312685671</v>
       </c>
       <c r="F30">
-        <v>1.02833666599025</v>
+        <v>0.9888616373156404</v>
       </c>
       <c r="G30">
-        <v>1.74028301487857</v>
+        <v>1.428286618566825</v>
       </c>
       <c r="H30">
-        <v>2.958695822329901</v>
+        <v>3.020095397011059</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.7989540359598912</v>
+        <v>0.7989540332012236</v>
       </c>
       <c r="C31">
-        <v>0.7988903312307788</v>
+        <v>0.7988485356850726</v>
       </c>
       <c r="D31">
-        <v>0.7986756190053909</v>
+        <v>0.7986898940174763</v>
       </c>
       <c r="E31">
-        <v>0.7755347742146675</v>
+        <v>0.7756250446391307</v>
       </c>
       <c r="F31">
-        <v>0.7965447539218193</v>
+        <v>0.7970792470299045</v>
       </c>
       <c r="G31">
-        <v>0.7958949023008576</v>
+        <v>0.7953223749761179</v>
       </c>
       <c r="H31">
-        <v>0.7960869473486685</v>
+        <v>0.7911846236185618</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1320,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>6.845550273635537E-09</v>
+        <v>1.014412049010932E-08</v>
       </c>
       <c r="D32">
-        <v>2.385678459289115E-08</v>
+        <v>3.796659759090174E-08</v>
       </c>
       <c r="E32">
-        <v>1.78485712277482E-07</v>
+        <v>6.374381037533606E-07</v>
       </c>
       <c r="F32">
-        <v>0.01041157254141545</v>
+        <v>0.5565034967611575</v>
       </c>
       <c r="G32">
-        <v>0.7743001060407263</v>
+        <v>0.7743000898614394</v>
       </c>
       <c r="H32">
-        <v>0.7750326380726607</v>
+        <v>0.7750326083111952</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.02366697796189705</v>
+        <v>0.02366697550539227</v>
       </c>
       <c r="C33">
-        <v>0.02366697930170042</v>
+        <v>0.02366697737037497</v>
       </c>
       <c r="D33">
-        <v>0.02366697426774633</v>
+        <v>0.0236669704374106</v>
       </c>
       <c r="E33">
-        <v>0.02366697110757341</v>
+        <v>0.0236669656948016</v>
       </c>
       <c r="F33">
-        <v>0.02366696147004623</v>
+        <v>0.02363668017304543</v>
       </c>
       <c r="G33">
-        <v>0.02357792366205292</v>
+        <v>0.02357791523568424</v>
       </c>
       <c r="H33">
-        <v>0.02366129342245745</v>
+        <v>0.02366115632018964</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>1.202444945569434E-08</v>
+        <v>1.773778418790093E-08</v>
       </c>
       <c r="D34">
-        <v>1.485405852267069E-08</v>
+        <v>2.231530108786893E-08</v>
       </c>
       <c r="E34">
-        <v>3.107797542090774E-08</v>
+        <v>4.690289823862972E-08</v>
       </c>
       <c r="F34">
-        <v>4.480039964911716E-08</v>
+        <v>6.66317417331623E-08</v>
       </c>
       <c r="G34">
-        <v>5.856982971727297E-08</v>
+        <v>8.929063716962656E-08</v>
       </c>
       <c r="H34">
-        <v>3.252829681327111E-07</v>
+        <v>4.969916427857275E-07</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1395,25 +1395,25 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.0247836560963707</v>
+        <v>0.02478365608870325</v>
       </c>
       <c r="C35">
-        <v>0.02478365359954995</v>
+        <v>0.02478365239444659</v>
       </c>
       <c r="D35">
-        <v>0.02478365218800383</v>
+        <v>0.02478365025521636</v>
       </c>
       <c r="E35">
-        <v>0.02478337115650053</v>
+        <v>0.02478319481547241</v>
       </c>
       <c r="F35">
-        <v>0.02478364392547686</v>
+        <v>0.02478363376075457</v>
       </c>
       <c r="G35">
-        <v>0.02478363604291535</v>
+        <v>0.02478361549413197</v>
       </c>
       <c r="H35">
-        <v>0.02478338884344654</v>
+        <v>0.02478238762060024</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1424,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>1.8454663161365E-07</v>
+        <v>2.675908757169119E-07</v>
       </c>
       <c r="D36">
-        <v>1.768457732433989E-07</v>
+        <v>2.559789988653999E-07</v>
       </c>
       <c r="E36">
-        <v>2.11166164684243E-05</v>
+        <v>1.582286763557087E-05</v>
       </c>
       <c r="F36">
-        <v>2.224642180267608E-05</v>
+        <v>1.651202530733546E-05</v>
       </c>
       <c r="G36">
-        <v>2.258445416326612E-05</v>
+        <v>1.657691695638326E-05</v>
       </c>
       <c r="H36">
-        <v>2.043357517329715E-05</v>
+        <v>1.442989042373691E-05</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>1.064229333490686</v>
+        <v>1.064229328364208</v>
       </c>
       <c r="C37">
-        <v>1.048722721647591</v>
+        <v>1.046928052417091</v>
       </c>
       <c r="D37">
-        <v>1.010582780713948</v>
+        <v>1.009878213578563</v>
       </c>
       <c r="E37">
-        <v>0.9047412220232462</v>
+        <v>0.8960266084529319</v>
       </c>
       <c r="F37">
-        <v>1.00804440995074</v>
+        <v>1.008373125861395</v>
       </c>
       <c r="G37">
-        <v>1.036694122960393</v>
+        <v>1.029923382160784</v>
       </c>
       <c r="H37">
-        <v>1.056432586866297</v>
+        <v>1.038257983364883</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.0005058111235023171</v>
+        <v>0.0005058214728201283</v>
       </c>
       <c r="C38">
-        <v>0.01616719651968784</v>
+        <v>0.01804627362110113</v>
       </c>
       <c r="D38">
-        <v>0.05477258588683367</v>
+        <v>0.05542863989544723</v>
       </c>
       <c r="E38">
-        <v>0.206911613995995</v>
+        <v>0.214320883334381</v>
       </c>
       <c r="F38">
-        <v>0.379567606045917</v>
+        <v>0.4151922748014024</v>
       </c>
       <c r="G38">
-        <v>0.7106675154698584</v>
+        <v>0.6604873222020323</v>
       </c>
       <c r="H38">
-        <v>1.483102168303365</v>
+        <v>1.781099366220193</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>0.6002003223539482</v>
+        <v>0.5876503923321814</v>
       </c>
       <c r="C40">
-        <v>0.7427717040711697</v>
+        <v>0.7559002380468152</v>
       </c>
       <c r="D40">
-        <v>1.096219332205498</v>
+        <v>1.09731161948801</v>
       </c>
       <c r="E40">
-        <v>1.052691886822191</v>
+        <v>1.018373190025714</v>
       </c>
       <c r="F40">
-        <v>1.094859627431672</v>
+        <v>1.094356792509715</v>
       </c>
       <c r="G40">
-        <v>1.230152348462189</v>
+        <v>1.216824264829398</v>
       </c>
       <c r="H40">
-        <v>1.402615425797705</v>
+        <v>1.671775126027371</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0.4801602606193032</v>
+        <v>0.4701203178848938</v>
       </c>
       <c r="C41">
-        <v>0.5942173657183395</v>
+        <v>0.6047201941079435</v>
       </c>
       <c r="D41">
-        <v>0.8769754723465863</v>
+        <v>0.8778493052230409</v>
       </c>
       <c r="E41">
-        <v>0.8421535233741979</v>
+        <v>0.8146985709471757</v>
       </c>
       <c r="F41">
-        <v>0.8758877530407687</v>
+        <v>0.8754855023953124</v>
       </c>
       <c r="G41">
-        <v>0.9841221525814534</v>
+        <v>0.9734596415149852</v>
       </c>
       <c r="H41">
-        <v>1.133242812853794</v>
+        <v>1.361920635314414</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-0.1200400617346449</v>
+        <v>-0.1175300744472876</v>
       </c>
       <c r="C42">
-        <v>-0.1485543383528302</v>
+        <v>-0.1511800439388716</v>
       </c>
       <c r="D42">
-        <v>-0.2192438598589113</v>
+        <v>-0.2194623142649694</v>
       </c>
       <c r="E42">
-        <v>-0.2105383634479934</v>
+        <v>-0.2036746190785381</v>
       </c>
       <c r="F42">
-        <v>-0.2189718743909033</v>
+        <v>-0.2188712901144024</v>
       </c>
       <c r="G42">
-        <v>-0.2460301958807356</v>
+        <v>-0.2433646233144127</v>
       </c>
       <c r="H42">
-        <v>-0.2693726129439109</v>
+        <v>-0.3098544907129568</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1603,25 +1603,25 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>-2.700476468224684</v>
+        <v>-2.700914776275267</v>
       </c>
       <c r="C43">
-        <v>-1.301470976640789</v>
+        <v>-1.490239989381849</v>
       </c>
       <c r="D43">
-        <v>-1.570083056851753</v>
+        <v>-1.690976746362676</v>
       </c>
       <c r="E43">
-        <v>-0.1527084862012743</v>
+        <v>-0.02637376803938242</v>
       </c>
       <c r="F43">
-        <v>-0.6070297651864058</v>
+        <v>-1.142245930288459</v>
       </c>
       <c r="G43">
-        <v>-1.597311911057866</v>
+        <v>-1.096588598402602</v>
       </c>
       <c r="H43">
-        <v>-2.7619592141019</v>
+        <v>-2.71336404010681</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1629,25 +1629,25 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>2.016867282311904</v>
+        <v>2.010621424551001</v>
       </c>
       <c r="C44">
-        <v>-0.1569373354002208</v>
+        <v>-0.1522291166771839</v>
       </c>
       <c r="D44">
-        <v>0.3210888846576449</v>
+        <v>0.3133695912948958</v>
       </c>
       <c r="E44">
-        <v>0.5633382419054042</v>
+        <v>0.5655632893336348</v>
       </c>
       <c r="F44">
-        <v>0.01798460675691948</v>
+        <v>-0.06656874463984903</v>
       </c>
       <c r="G44">
-        <v>-0.9817513132162657</v>
+        <v>-0.8230488807210009</v>
       </c>
       <c r="H44">
-        <v>-2.600378636287847</v>
+        <v>-2.544343031265254</v>
       </c>
     </row>
   </sheetData>
